--- a/Final Results Compiled/embedding_comparison_report.xlsx
+++ b/Final Results Compiled/embedding_comparison_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MS-MLAI-UpGrad\Research Things\LJMU Thesis\HotPotQA-Coding-Trials\Final Results Compiled\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D4EA77-E503-4952-B32E-89EC7C98F745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADBA1ED-0E1C-42AA-9D66-275DDB128413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -341,11 +341,11 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,26 +728,26 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
@@ -760,7 +760,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="13">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>20</v>
@@ -804,26 +804,26 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
@@ -836,7 +836,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>20</v>
@@ -888,7 +888,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>23</v>
@@ -940,7 +940,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>24</v>
@@ -992,7 +992,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>25</v>
@@ -1044,7 +1044,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>26</v>
@@ -1086,26 +1086,26 @@
       <c r="R9" s="5"/>
     </row>
     <row r="11" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
     </row>
     <row r="12" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
@@ -1118,7 +1118,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>20</v>
@@ -1170,7 +1170,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>23</v>
@@ -1222,7 +1222,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>24</v>
@@ -1274,7 +1274,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>25</v>
@@ -1326,7 +1326,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>26</v>
@@ -1368,26 +1368,26 @@
       <c r="R16" s="5"/>
     </row>
     <row r="18" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
     </row>
     <row r="19" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
@@ -1400,7 +1400,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>20</v>
@@ -1452,7 +1452,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>23</v>
@@ -1504,7 +1504,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>24</v>
@@ -1556,7 +1556,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>25</v>
@@ -1608,7 +1608,7 @@
         <v>19</v>
       </c>
       <c r="D23" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>26</v>
@@ -1650,26 +1650,26 @@
       <c r="R23" s="5"/>
     </row>
     <row r="25" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
     </row>
     <row r="26" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
@@ -1682,7 +1682,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>20</v>
@@ -1734,7 +1734,7 @@
         <v>19</v>
       </c>
       <c r="D27" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>23</v>
@@ -1786,7 +1786,7 @@
         <v>19</v>
       </c>
       <c r="D28" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>24</v>
@@ -1838,7 +1838,7 @@
         <v>19</v>
       </c>
       <c r="D29" s="7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>25</v>
@@ -1890,7 +1890,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>26</v>
@@ -1932,39 +1932,39 @@
       <c r="R30" s="5"/>
     </row>
     <row r="32" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
     </row>
     <row r="33" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>26</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>20</v>
@@ -2009,14 +2009,14 @@
       <c r="A34" s="5">
         <v>27</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>23</v>
@@ -2061,14 +2061,14 @@
       <c r="A35" s="5">
         <v>28</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>24</v>
@@ -2113,14 +2113,14 @@
       <c r="A36" s="3">
         <v>29</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>25</v>
@@ -2165,14 +2165,14 @@
       <c r="A37" s="5">
         <v>30</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>26</v>

--- a/Final Results Compiled/embedding_comparison_report.xlsx
+++ b/Final Results Compiled/embedding_comparison_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MS-MLAI-UpGrad\Research Things\LJMU Thesis\HotPotQA-Coding-Trials\Final Results Compiled\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADBA1ED-0E1C-42AA-9D66-275DDB128413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3839A3EC-F5E9-418D-B29D-53C66D6BE4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,28 +203,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,6 +234,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -299,13 +285,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -332,20 +315,29 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,24 +643,25 @@
   <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="22" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
-    <col min="18" max="18" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" style="12" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="12" customWidth="1"/>
+    <col min="4" max="4" width="18" style="12" customWidth="1"/>
+    <col min="5" max="5" width="26" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12" style="12" customWidth="1"/>
+    <col min="7" max="7" width="22" style="12" customWidth="1"/>
+    <col min="8" max="8" width="12" style="12" customWidth="1"/>
+    <col min="9" max="9" width="8" style="12" customWidth="1"/>
+    <col min="10" max="10" width="14" style="12" customWidth="1"/>
+    <col min="11" max="11" width="8" style="12" customWidth="1"/>
+    <col min="12" max="12" width="13" style="12" customWidth="1"/>
+    <col min="13" max="13" width="11" style="12" customWidth="1"/>
+    <col min="14" max="14" width="16" style="12" customWidth="1"/>
+    <col min="15" max="15" width="10" style="12" customWidth="1"/>
+    <col min="16" max="16" width="22" style="12" customWidth="1"/>
+    <col min="17" max="17" width="10" style="12" customWidth="1"/>
+    <col min="18" max="18" width="28.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -728,1499 +721,1499 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
     </row>
     <row r="3" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="13">
-        <v>500</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="C3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="17">
+        <v>500</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="14">
+      <c r="G3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="18">
         <v>0.36</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="18">
         <v>0.47539999999999999</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="18">
         <v>0.15</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="18">
         <v>0.51470000000000005</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="18">
         <v>0.64329999999999998</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="18">
         <v>0.45729999999999998</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="18">
         <v>0.1</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="18">
         <v>0.31490000000000001</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="18">
         <v>0.54300000000000004</v>
       </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2" t="s">
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
     </row>
     <row r="5" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="15">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3">
-        <v>500</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2">
+        <v>500</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="3">
         <v>0.36</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>0.46350000000000002</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>0.11</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>0.46429999999999999</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>0.58830000000000005</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
         <v>0.40649999999999997</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="3">
         <v>0.30020000000000002</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="3">
         <v>0.59419999999999995</v>
       </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="15">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5">
-        <v>500</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4">
+        <v>500</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="F6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5">
         <v>0.33</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>0.47260000000000002</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>0.51580000000000004</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>0.67500000000000004</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>0.44400000000000001</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <v>0.32019999999999998</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>0.64170000000000005</v>
       </c>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
     </row>
     <row r="7" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="15">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="5">
-        <v>500</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>500</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5">
         <v>0.37</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>0.51859999999999995</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>0.22</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>0.61409999999999998</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>0.73170000000000002</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>0.56030000000000002</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>0.13</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <v>0.38979999999999998</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>0.70309999999999995</v>
       </c>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
     </row>
     <row r="8" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+      <c r="A8" s="15">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7">
-        <v>500</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6">
+        <v>500</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="F8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="7">
         <v>0.42</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>0.56820000000000004</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="7">
         <v>0.63009999999999999</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="7">
         <v>0.745</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="7">
         <v>0.57450000000000001</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="7">
         <v>0.19</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="7">
         <v>0.44729999999999998</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="7">
         <v>0.71330000000000005</v>
       </c>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
     </row>
     <row r="9" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="15">
         <v>10</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="5">
-        <v>500</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>500</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="F9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="5">
         <v>0.36</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>0.48749999999999999</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>0.16</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>0.51929999999999998</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>0.66749999999999998</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>0.45569999999999999</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>0.1</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>0.33019999999999999</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <v>0.61329999999999996</v>
       </c>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
     </row>
     <row r="11" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
     </row>
     <row r="12" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="15">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3">
-        <v>500</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2">
+        <v>500</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="4">
+      <c r="F12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="3">
         <v>0.35</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="3">
         <v>0.4894</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="3">
         <v>0.21</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="3">
         <v>0.54310000000000003</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="3">
         <v>0.64080000000000004</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M12" s="3">
         <v>0.50570000000000004</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N12" s="3">
         <v>0.13</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O12" s="3">
         <v>0.34599999999999997</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="3">
         <v>0.65069999999999995</v>
       </c>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="A13" s="15">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="5">
-        <v>500</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="4">
+        <v>500</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="F13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="5">
         <v>0.44</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>0.58730000000000004</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="5">
         <v>0.22</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>0.5786</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>0.7117</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>0.51729999999999998</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O13" s="6">
+      <c r="O13" s="5">
         <v>0.41899999999999998</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="5">
         <v>0.6492</v>
       </c>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
     </row>
     <row r="14" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+      <c r="A14" s="15">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="5">
-        <v>500</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="C14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <v>500</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="6">
+      <c r="F14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="5">
         <v>0.45</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>0.58660000000000001</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>0.32</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>0.64180000000000004</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>0.72250000000000003</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>0.60229999999999995</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="5">
         <v>0.17</v>
       </c>
-      <c r="O14" s="6">
+      <c r="O14" s="5">
         <v>0.4476</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="5">
         <v>0.77110000000000001</v>
       </c>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+      <c r="A15" s="15">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="7">
-        <v>500</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="C15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="6">
+        <v>500</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="F15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="7">
         <v>0.45</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <v>0.60970000000000002</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="7">
         <v>0.31</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="7">
         <v>0.62890000000000001</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="7">
         <v>0.72170000000000001</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="7">
         <v>0.58479999999999999</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="7">
         <v>0.19</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="7">
         <v>0.45910000000000001</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="7">
         <v>0.70399999999999996</v>
       </c>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
     </row>
     <row r="16" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="A16" s="15">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="5">
-        <v>500</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="C16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="4">
+        <v>500</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="6">
+      <c r="F16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="5">
         <v>0.38</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>0.53320000000000001</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <v>0.21</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>0.56089999999999995</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <v>0.66830000000000001</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>0.51149999999999995</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="5">
         <v>0.11</v>
       </c>
-      <c r="O16" s="6">
+      <c r="O16" s="5">
         <v>0.373</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="5">
         <v>0.60750000000000004</v>
       </c>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
     </row>
     <row r="18" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
     </row>
     <row r="19" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="15">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="5">
-        <v>500</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="C19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="4">
+        <v>500</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="6">
+      <c r="F19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="5">
         <v>0.41</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>0.51300000000000001</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="5">
         <v>0.18</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>0.56659999999999999</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>0.6875</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>0.51819999999999999</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="5">
         <v>0.12</v>
       </c>
-      <c r="O19" s="6">
+      <c r="O19" s="5">
         <v>0.35859999999999997</v>
       </c>
-      <c r="P19" s="6">
+      <c r="P19" s="5">
         <v>0.61919999999999997</v>
       </c>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
     </row>
     <row r="20" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="15">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="3">
-        <v>500</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="C20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2">
+        <v>500</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="4">
+      <c r="F20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="3">
         <v>0.38</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="3">
         <v>0.51139999999999997</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="3">
         <v>0.21</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="3">
         <v>0.56640000000000001</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="3">
         <v>0.69079999999999997</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M20" s="3">
         <v>0.51400000000000001</v>
       </c>
-      <c r="N20" s="4">
+      <c r="N20" s="3">
         <v>0.13</v>
       </c>
-      <c r="O20" s="4">
+      <c r="O20" s="3">
         <v>0.35089999999999999</v>
       </c>
-      <c r="P20" s="4">
+      <c r="P20" s="3">
         <v>0.63719999999999999</v>
       </c>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="15">
         <v>18</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="5">
-        <v>500</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="C21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="4">
+        <v>500</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="6">
+      <c r="F21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="5">
         <v>0.42</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>0.52649999999999997</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="5">
         <v>0.21</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>0.56779999999999997</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>0.70499999999999996</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>0.51149999999999995</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="5">
         <v>0.37030000000000002</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="5">
         <v>0.65249999999999997</v>
       </c>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
     </row>
     <row r="22" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
-        <v>19</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="A22" s="15">
+        <v>19</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="7">
-        <v>500</v>
-      </c>
-      <c r="E22" s="7" t="s">
+      <c r="C22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="6">
+        <v>500</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="8">
+      <c r="F22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="7">
         <v>0.42</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="7">
         <v>0.56899999999999995</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="7">
         <v>0.24</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="7">
         <v>0.60970000000000002</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="7">
         <v>0.71750000000000003</v>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="7">
         <v>0.56320000000000003</v>
       </c>
-      <c r="N22" s="8">
+      <c r="N22" s="7">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O22" s="8">
+      <c r="O22" s="7">
         <v>0.42320000000000002</v>
       </c>
-      <c r="P22" s="8">
+      <c r="P22" s="7">
         <v>0.65790000000000004</v>
       </c>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
     </row>
     <row r="23" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="A23" s="15">
         <v>20</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="5">
-        <v>500</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="C23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="4">
+        <v>500</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="6">
+      <c r="F23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="5">
         <v>0.39</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>0.51259999999999994</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="5">
         <v>0.17</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>0.5524</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>0.69330000000000003</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>0.49480000000000002</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="5">
         <v>0.1</v>
       </c>
-      <c r="O23" s="6">
+      <c r="O23" s="5">
         <v>0.34329999999999999</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="5">
         <v>0.61450000000000005</v>
       </c>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
     </row>
     <row r="25" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
     </row>
     <row r="26" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
-        <v>21</v>
-      </c>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="15">
+        <v>21</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="5">
-        <v>500</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="C26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="4">
+        <v>500</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="6">
+      <c r="F26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="5">
         <v>0.43</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="5">
         <v>0.55030000000000001</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="5">
         <v>0.22</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <v>0.58140000000000003</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="5">
         <v>0.69420000000000004</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="5">
         <v>0.53400000000000003</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="5">
         <v>0.11</v>
       </c>
-      <c r="O26" s="6">
+      <c r="O26" s="5">
         <v>0.39850000000000002</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="5">
         <v>0.68079999999999996</v>
       </c>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
     </row>
     <row r="27" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>22</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="15">
+        <v>22</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="3">
-        <v>500</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="C27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="2">
+        <v>500</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="F27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="3">
         <v>0.4</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="3">
         <v>0.5474</v>
       </c>
-      <c r="J27" s="4">
+      <c r="J27" s="3">
         <v>0.21</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="3">
         <v>0.58879999999999999</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="3">
         <v>0.71499999999999997</v>
       </c>
-      <c r="M27" s="4">
+      <c r="M27" s="3">
         <v>0.53569999999999995</v>
       </c>
-      <c r="N27" s="4">
+      <c r="N27" s="3">
         <v>0.1</v>
       </c>
-      <c r="O27" s="4">
+      <c r="O27" s="3">
         <v>0.39069999999999999</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27" s="3">
         <v>0.67090000000000005</v>
       </c>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="A28" s="15">
         <v>23</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="5">
-        <v>500</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="C28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="4">
+        <v>500</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="6">
+      <c r="F28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="5">
         <v>0.42</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="5">
         <v>0.55940000000000001</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="5">
         <v>0.25</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>0.59150000000000003</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>0.7</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>0.54069999999999996</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O28" s="6">
+      <c r="O28" s="5">
         <v>0.41739999999999999</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="5">
         <v>0.69579999999999997</v>
       </c>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
     </row>
     <row r="29" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
+      <c r="A29" s="15">
         <v>24</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="7">
-        <v>500</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="C29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="6">
+        <v>500</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="8">
+      <c r="F29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="7">
         <v>0.44</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="7">
         <v>0.58989999999999998</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="7">
         <v>0.27</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="7">
         <v>0.61050000000000004</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="7">
         <v>0.71</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="7">
         <v>0.56320000000000003</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="7">
         <v>0.15</v>
       </c>
-      <c r="O29" s="8">
+      <c r="O29" s="7">
         <v>0.44359999999999999</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="7">
         <v>0.67830000000000001</v>
       </c>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
     </row>
     <row r="30" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="A30" s="15">
         <v>25</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="5">
-        <v>500</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="C30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="4">
+        <v>500</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="6">
+      <c r="F30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="5">
         <v>0.41</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="5">
         <v>0.56220000000000003</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="5">
         <v>0.23</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>0.61009999999999998</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>0.73080000000000001</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>0.55479999999999996</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="5">
         <v>0.12</v>
       </c>
-      <c r="O30" s="6">
+      <c r="O30" s="5">
         <v>0.41199999999999998</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="5">
         <v>0.6542</v>
       </c>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
     </row>
     <row r="32" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
     </row>
     <row r="33" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
+      <c r="A33" s="15">
         <v>26</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="7">
-        <v>500</v>
-      </c>
-      <c r="E33" s="7" t="s">
+      <c r="C33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="6">
+        <v>500</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="8">
+      <c r="F33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="7">
         <v>0.52</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="7">
         <v>0.64849999999999997</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="7">
         <v>0.21</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="7">
         <v>0.629</v>
       </c>
-      <c r="L33" s="8">
+      <c r="L33" s="7">
         <v>0.74419999999999997</v>
       </c>
-      <c r="M33" s="8">
+      <c r="M33" s="7">
         <v>0.57069999999999999</v>
       </c>
-      <c r="N33" s="8">
+      <c r="N33" s="7">
         <v>0.15</v>
       </c>
-      <c r="O33" s="8">
+      <c r="O33" s="7">
         <v>0.47189999999999999</v>
       </c>
-      <c r="P33" s="8">
+      <c r="P33" s="7">
         <v>0.74450000000000005</v>
       </c>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
     </row>
     <row r="34" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+      <c r="A34" s="15">
         <v>27</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="5">
-        <v>500</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="C34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="4">
+        <v>500</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="6">
+      <c r="F34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="5">
         <v>0.47</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <v>0.63339999999999996</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <v>0.27</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <v>0.63900000000000001</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <v>0.745</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>0.59230000000000005</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O34" s="6">
+      <c r="O34" s="5">
         <v>0.4647</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="5">
         <v>0.7601</v>
       </c>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
     </row>
     <row r="35" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+      <c r="A35" s="15">
         <v>28</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="5">
-        <v>500</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="4">
+        <v>500</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="6">
+      <c r="F35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="5">
         <v>0.5</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <v>0.64810000000000001</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="5">
         <v>0.27</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>0.63839999999999997</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>0.74580000000000002</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="5">
         <v>0.58399999999999996</v>
       </c>
-      <c r="N35" s="6">
+      <c r="N35" s="5">
         <v>0.17</v>
       </c>
-      <c r="O35" s="6">
+      <c r="O35" s="5">
         <v>0.47449999999999998</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="5">
         <v>0.67330000000000001</v>
       </c>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
     </row>
     <row r="36" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="A36" s="15">
         <v>29</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="3">
-        <v>500</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="C36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="2">
+        <v>500</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" s="4">
+      <c r="F36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="3">
         <v>0.45</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="3">
         <v>0.61450000000000005</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J36" s="3">
         <v>0.27</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K36" s="3">
         <v>0.60840000000000005</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="3">
         <v>0.71330000000000005</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M36" s="3">
         <v>0.56030000000000002</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="3">
         <v>0.15</v>
       </c>
-      <c r="O36" s="4">
+      <c r="O36" s="3">
         <v>0.43259999999999998</v>
       </c>
-      <c r="P36" s="4">
+      <c r="P36" s="3">
         <v>0.7167</v>
       </c>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
     </row>
     <row r="37" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="A37" s="15">
         <v>30</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="5">
-        <v>500</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="C37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="4">
+        <v>500</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="6">
+      <c r="F37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="5">
         <v>0.48</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="5">
         <v>0.63029999999999997</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="5">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="5">
         <v>0.62870000000000004</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="5">
         <v>0.74170000000000003</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="5">
         <v>0.57650000000000001</v>
       </c>
-      <c r="N37" s="6">
+      <c r="N37" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O37" s="6">
+      <c r="O37" s="5">
         <v>0.46479999999999999</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="5">
         <v>0.67600000000000005</v>
       </c>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="10" t="s">
         <v>37</v>
       </c>
     </row>
